--- a/Data/Inputs/grupos_alimentos.xlsx
+++ b/Data/Inputs/grupos_alimentos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\OneDrive\Escritorio\Maestria\14. Proyecto integrador\Git\ProyectoIntegradorSep24_Grupo15\Data\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30D5A05E-1095-46FC-BE81-B3AC3D568035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47346C2F-18D4-48DA-B14B-8690BA07C452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="224">
   <si>
     <t>alimento</t>
   </si>
@@ -692,6 +692,9 @@
   </si>
   <si>
     <t>Cereales</t>
+  </si>
+  <si>
+    <t>Otro</t>
   </si>
 </sst>
 </file>
@@ -2136,7 +2139,7 @@
         <v>66</v>
       </c>
       <c r="C98" t="s">
-        <v>66</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.4">
@@ -2147,7 +2150,7 @@
         <v>66</v>
       </c>
       <c r="C99" t="s">
-        <v>66</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.4">
@@ -2554,7 +2557,7 @@
         <v>66</v>
       </c>
       <c r="C136" t="s">
-        <v>66</v>
+        <v>223</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.4">
@@ -2939,7 +2942,7 @@
         <v>66</v>
       </c>
       <c r="C171" t="s">
-        <v>66</v>
+        <v>223</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.4">
@@ -3126,7 +3129,7 @@
         <v>66</v>
       </c>
       <c r="C188" t="s">
-        <v>66</v>
+        <v>223</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.4">
@@ -3137,7 +3140,7 @@
         <v>66</v>
       </c>
       <c r="C189" t="s">
-        <v>66</v>
+        <v>223</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.4">
